--- a/02-Execucao/05-Comentarios_Gestor/03-Produtos_Pos_Comentarios/impactos-comentarios-gestor.xlsx
+++ b/02-Execucao/05-Comentarios_Gestor/03-Produtos_Pos_Comentarios/impactos-comentarios-gestor.xlsx
@@ -807,10 +807,10 @@
         <v>18</v>
       </c>
       <c r="C3">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D3">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E3">
         <v>5</v>
@@ -825,10 +825,10 @@
         <v>0.4338685236850021</v>
       </c>
       <c r="I3">
-        <v>0.4793019068684717</v>
+        <v>0.4940729802266843</v>
       </c>
       <c r="J3">
-        <v>0.04543338318346957</v>
+        <v>0.06020445654168216</v>
       </c>
     </row>
     <row r="4" spans="1:10">
@@ -1223,10 +1223,10 @@
         <v>20</v>
       </c>
       <c r="C16">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="D16">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E16">
         <v>5</v>
@@ -2293,10 +2293,10 @@
         <v>18</v>
       </c>
       <c r="C50">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D50">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E50">
         <v>6</v>
@@ -2311,10 +2311,10 @@
         <v>0.4407467228894335</v>
       </c>
       <c r="I50">
-        <v>0.4543064625116398</v>
+        <v>0.4610863323227429</v>
       </c>
       <c r="J50">
-        <v>0.0135597396222063</v>
+        <v>0.02033960943330937</v>
       </c>
     </row>
     <row r="51" spans="1:10">
@@ -2485,10 +2485,10 @@
         <v>20</v>
       </c>
       <c r="C56">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D56">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E56">
         <v>5</v>
@@ -2645,10 +2645,10 @@
         <v>10</v>
       </c>
       <c r="C61">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D61">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E61">
         <v>3</v>
@@ -2663,10 +2663,10 @@
         <v>0.6571131403027882</v>
       </c>
       <c r="I61">
-        <v>0.7174889157660744</v>
+        <v>0.7102982000691678</v>
       </c>
       <c r="J61">
-        <v>0.06037577546328621</v>
+        <v>0.05318505976637955</v>
       </c>
     </row>
     <row r="62" spans="1:10">
@@ -3459,10 +3459,10 @@
         <v>14</v>
       </c>
       <c r="C87">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D87">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E87">
         <v>5</v>
@@ -3779,10 +3779,10 @@
         <v>20</v>
       </c>
       <c r="C97">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="D97">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E97">
         <v>6</v>
@@ -4035,10 +4035,10 @@
         <v>0.730627879068066</v>
       </c>
       <c r="I105">
-        <v>0.751109300909877</v>
+        <v>0.7545689962328395</v>
       </c>
       <c r="J105">
-        <v>0.02048142184181101</v>
+        <v>0.02394111716477343</v>
       </c>
     </row>
     <row r="106" spans="1:10">
@@ -4081,19 +4081,19 @@
         <v>21</v>
       </c>
       <c r="C107">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="D107">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E107">
         <v>6</v>
       </c>
       <c r="F107">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G107">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H107">
         <v>0.1128734585880629</v>
@@ -4241,10 +4241,10 @@
         <v>22</v>
       </c>
       <c r="C112">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D112">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E112">
         <v>6</v>
@@ -4291,10 +4291,10 @@
         <v>0.2143910869258308</v>
       </c>
       <c r="I113">
-        <v>0.2422405963216705</v>
+        <v>0.2446157937919437</v>
       </c>
       <c r="J113">
-        <v>0.02784950939583969</v>
+        <v>0.03022470686611289</v>
       </c>
     </row>
     <row r="114" spans="1:10">
@@ -4305,10 +4305,10 @@
         <v>18</v>
       </c>
       <c r="C114">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D114">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E114">
         <v>6</v>
@@ -4465,10 +4465,10 @@
         <v>19</v>
       </c>
       <c r="C119">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D119">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E119">
         <v>5</v>

--- a/02-Execucao/05-Comentarios_Gestor/03-Produtos_Pos_Comentarios/impactos-comentarios-gestor.xlsx
+++ b/02-Execucao/05-Comentarios_Gestor/03-Produtos_Pos_Comentarios/impactos-comentarios-gestor.xlsx
@@ -807,10 +807,10 @@
         <v>18</v>
       </c>
       <c r="C3">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D3">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E3">
         <v>5</v>
@@ -825,10 +825,10 @@
         <v>0.4338685236850021</v>
       </c>
       <c r="I3">
-        <v>0.4940729802266843</v>
+        <v>0.4872931104155812</v>
       </c>
       <c r="J3">
-        <v>0.06020445654168216</v>
+        <v>0.05342458673057909</v>
       </c>
     </row>
     <row r="4" spans="1:10">
@@ -999,10 +999,10 @@
         <v>21</v>
       </c>
       <c r="C9">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D9">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E9">
         <v>6</v>
@@ -1063,10 +1063,10 @@
         <v>19</v>
       </c>
       <c r="C11">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="D11">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E11">
         <v>5</v>
@@ -1159,10 +1159,10 @@
         <v>19</v>
       </c>
       <c r="C14">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="D14">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E14">
         <v>5</v>
@@ -1241,10 +1241,10 @@
         <v>0.1576795157441079</v>
       </c>
       <c r="I16">
-        <v>0.1637617224210189</v>
+        <v>0.16984392909793</v>
       </c>
       <c r="J16">
-        <v>0.006082206676911006</v>
+        <v>0.0121644133538221</v>
       </c>
     </row>
     <row r="17" spans="1:10">
@@ -1360,10 +1360,10 @@
         <v>0.2580680375751482</v>
       </c>
       <c r="I20">
-        <v>0.2580680375751482</v>
+        <v>0.2610474713125606</v>
       </c>
       <c r="J20">
-        <v>0</v>
+        <v>0.00297943373741244</v>
       </c>
     </row>
     <row r="21" spans="1:10">
@@ -1927,10 +1927,10 @@
         <v>0.1533646449096753</v>
       </c>
       <c r="I38">
-        <v>0.1695055871036197</v>
+        <v>0.1762854569147228</v>
       </c>
       <c r="J38">
-        <v>0.01614094219394441</v>
+        <v>0.0229208120050475</v>
       </c>
     </row>
     <row r="39" spans="1:10">
@@ -2037,10 +2037,10 @@
         <v>18</v>
       </c>
       <c r="C42">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D42">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E42">
         <v>5</v>
@@ -2055,10 +2055,10 @@
         <v>0.06955825063336939</v>
       </c>
       <c r="I42">
-        <v>0.07451357038173305</v>
+        <v>0.07549159286949259</v>
       </c>
       <c r="J42">
-        <v>0.004955319748363662</v>
+        <v>0.005933342236123199</v>
       </c>
     </row>
     <row r="43" spans="1:10">
@@ -2229,10 +2229,10 @@
         <v>15</v>
       </c>
       <c r="C48">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D48">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E48">
         <v>5</v>
@@ -2247,10 +2247,10 @@
         <v>0.2557711225891841</v>
       </c>
       <c r="I48">
-        <v>0.2852422625333925</v>
+        <v>0.2981958726924157</v>
       </c>
       <c r="J48">
-        <v>0.02947113994420841</v>
+        <v>0.0424247501032316</v>
       </c>
     </row>
     <row r="49" spans="1:10">
@@ -2261,10 +2261,10 @@
         <v>20</v>
       </c>
       <c r="C49">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="D49">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E49">
         <v>5</v>
@@ -2293,10 +2293,10 @@
         <v>18</v>
       </c>
       <c r="C50">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="D50">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="E50">
         <v>6</v>
@@ -2311,10 +2311,10 @@
         <v>0.4407467228894335</v>
       </c>
       <c r="I50">
-        <v>0.4610863323227429</v>
+        <v>0.4543064625116398</v>
       </c>
       <c r="J50">
-        <v>0.02033960943330937</v>
+        <v>0.0135597396222063</v>
       </c>
     </row>
     <row r="51" spans="1:10">
@@ -2357,10 +2357,10 @@
         <v>21</v>
       </c>
       <c r="C52">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D52">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E52">
         <v>6</v>
@@ -2485,10 +2485,10 @@
         <v>20</v>
       </c>
       <c r="C56">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="D56">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E56">
         <v>5</v>
@@ -2759,10 +2759,10 @@
         <v>0.1274362090162726</v>
       </c>
       <c r="I64">
-        <v>0.1335184156931837</v>
+        <v>0.1456828290470058</v>
       </c>
       <c r="J64">
-        <v>0.006082206676911117</v>
+        <v>0.01824662003073321</v>
       </c>
     </row>
     <row r="65" spans="1:10">
@@ -3020,10 +3020,10 @@
         <v>16</v>
       </c>
       <c r="C73">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D73">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E73">
         <v>6</v>
@@ -3084,10 +3084,10 @@
         <v>18</v>
       </c>
       <c r="C75">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="D75">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E75">
         <v>5</v>
@@ -3102,10 +3102,10 @@
         <v>0.2228808701329766</v>
       </c>
       <c r="I75">
-        <v>0.262986369033639</v>
+        <v>0.2524230168494018</v>
       </c>
       <c r="J75">
-        <v>0.04010549890066237</v>
+        <v>0.02954214671642522</v>
       </c>
     </row>
     <row r="76" spans="1:10">
@@ -3116,10 +3116,10 @@
         <v>17</v>
       </c>
       <c r="C76">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D76">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E76">
         <v>5</v>
@@ -3134,10 +3134,10 @@
         <v>0.3907341240311753</v>
       </c>
       <c r="I76">
-        <v>0.4330995802621066</v>
+        <v>0.5508217026140215</v>
       </c>
       <c r="J76">
-        <v>0.0423654562309313</v>
+        <v>0.1600875785828462</v>
       </c>
     </row>
     <row r="77" spans="1:10">
@@ -3459,10 +3459,10 @@
         <v>14</v>
       </c>
       <c r="C87">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D87">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E87">
         <v>5</v>
@@ -3846,7 +3846,7 @@
         <v>19</v>
       </c>
       <c r="D99">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E99">
         <v>6</v>
@@ -3962,10 +3962,10 @@
         <v>18</v>
       </c>
       <c r="C103">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D103">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E103">
         <v>5</v>
@@ -3980,10 +3980,10 @@
         <v>0.3511163912796449</v>
       </c>
       <c r="I103">
-        <v>0.35803578192557</v>
+        <v>0.3511163912796449</v>
       </c>
       <c r="J103">
-        <v>0.006919390645925116</v>
+        <v>0</v>
       </c>
     </row>
     <row r="104" spans="1:10">
@@ -4035,10 +4035,10 @@
         <v>0.730627879068066</v>
       </c>
       <c r="I105">
-        <v>0.7545689962328395</v>
+        <v>0.7578891707209801</v>
       </c>
       <c r="J105">
-        <v>0.02394111716477343</v>
+        <v>0.02726129165291402</v>
       </c>
     </row>
     <row r="106" spans="1:10">
@@ -4081,19 +4081,19 @@
         <v>21</v>
       </c>
       <c r="C107">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="D107">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="E107">
         <v>6</v>
       </c>
       <c r="F107">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G107">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H107">
         <v>0.1128734585880629</v>
@@ -4241,19 +4241,19 @@
         <v>22</v>
       </c>
       <c r="C112">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="D112">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="E112">
         <v>6</v>
       </c>
       <c r="F112">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G112">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H112">
         <v>0.1189423410704612</v>
@@ -4291,10 +4291,10 @@
         <v>0.2143910869258308</v>
       </c>
       <c r="I113">
-        <v>0.2446157937919437</v>
+        <v>0.2422405963216705</v>
       </c>
       <c r="J113">
-        <v>0.03022470686611289</v>
+        <v>0.02784950939583969</v>
       </c>
     </row>
     <row r="114" spans="1:10">
@@ -4305,10 +4305,10 @@
         <v>18</v>
       </c>
       <c r="C114">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D114">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E114">
         <v>6</v>
@@ -4323,10 +4323,10 @@
         <v>0.3787705980140124</v>
       </c>
       <c r="I114">
-        <v>0.3787705980140124</v>
+        <v>0.3811457954842856</v>
       </c>
       <c r="J114">
-        <v>0</v>
+        <v>0.002375197470273205</v>
       </c>
     </row>
     <row r="115" spans="1:10">

--- a/02-Execucao/05-Comentarios_Gestor/03-Produtos_Pos_Comentarios/impactos-comentarios-gestor.xlsx
+++ b/02-Execucao/05-Comentarios_Gestor/03-Produtos_Pos_Comentarios/impactos-comentarios-gestor.xlsx
@@ -772,19 +772,19 @@
         <v>10</v>
       </c>
       <c r="B2">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="C2">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="D2">
         <v>0</v>
       </c>
       <c r="E2">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F2">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G2">
         <v>0</v>
@@ -804,10 +804,10 @@
         <v>11</v>
       </c>
       <c r="B3">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="C3">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="D3">
         <v>6</v>
@@ -836,10 +836,10 @@
         <v>12</v>
       </c>
       <c r="B4">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="C4">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="D4">
         <v>0</v>
@@ -868,10 +868,10 @@
         <v>13</v>
       </c>
       <c r="B5">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="C5">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="D5">
         <v>0</v>
@@ -900,10 +900,10 @@
         <v>14</v>
       </c>
       <c r="B6">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="C6">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="D6">
         <v>1</v>
@@ -932,10 +932,10 @@
         <v>15</v>
       </c>
       <c r="B7">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="C7">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="D7">
         <v>0</v>
@@ -964,10 +964,10 @@
         <v>16</v>
       </c>
       <c r="B8">
-        <v>23</v>
+        <v>16</v>
       </c>
       <c r="C8">
-        <v>23</v>
+        <v>16</v>
       </c>
       <c r="D8">
         <v>0</v>
@@ -996,10 +996,10 @@
         <v>17</v>
       </c>
       <c r="B9">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="C9">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="D9">
         <v>2</v>
@@ -1028,10 +1028,10 @@
         <v>18</v>
       </c>
       <c r="B10">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="C10">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="D10">
         <v>0</v>
@@ -1060,10 +1060,10 @@
         <v>19</v>
       </c>
       <c r="B11">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="C11">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="D11">
         <v>1</v>
@@ -1092,10 +1092,10 @@
         <v>20</v>
       </c>
       <c r="B12">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="C12">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="D12">
         <v>0</v>
@@ -1124,13 +1124,13 @@
         <v>21</v>
       </c>
       <c r="B13">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="C13">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="D13">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E13">
         <v>5</v>
@@ -1156,19 +1156,19 @@
         <v>22</v>
       </c>
       <c r="B14">
-        <v>19</v>
+        <v>10</v>
       </c>
       <c r="C14">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="D14">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E14">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F14">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G14">
         <v>0</v>
@@ -1188,10 +1188,10 @@
         <v>23</v>
       </c>
       <c r="B15">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="C15">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="D15">
         <v>0</v>
@@ -1220,10 +1220,10 @@
         <v>24</v>
       </c>
       <c r="B16">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="C16">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="D16">
         <v>1</v>
@@ -1252,10 +1252,10 @@
         <v>25</v>
       </c>
       <c r="B17">
-        <v>20</v>
+        <v>11</v>
       </c>
       <c r="C17">
-        <v>20</v>
+        <v>11</v>
       </c>
       <c r="D17">
         <v>0</v>
@@ -1307,10 +1307,10 @@
         <v>27</v>
       </c>
       <c r="B19">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="C19">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="D19">
         <v>0</v>
@@ -1339,19 +1339,19 @@
         <v>28</v>
       </c>
       <c r="B20">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="C20">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="D20">
         <v>0</v>
       </c>
       <c r="E20">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="F20">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="G20">
         <v>0</v>
@@ -1371,19 +1371,19 @@
         <v>29</v>
       </c>
       <c r="B21">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="C21">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="D21">
+        <v>1</v>
+      </c>
+      <c r="E21">
         <v>3</v>
       </c>
-      <c r="E21">
-        <v>4</v>
-      </c>
       <c r="F21">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G21">
         <v>0</v>
@@ -1403,10 +1403,10 @@
         <v>30</v>
       </c>
       <c r="B22">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="C22">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="D22">
         <v>0</v>
@@ -1435,10 +1435,10 @@
         <v>31</v>
       </c>
       <c r="B23">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="C23">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="D23">
         <v>0</v>
@@ -1467,10 +1467,10 @@
         <v>32</v>
       </c>
       <c r="B24">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="C24">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="D24">
         <v>0</v>
@@ -1499,10 +1499,10 @@
         <v>33</v>
       </c>
       <c r="B25">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="C25">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="D25">
         <v>0</v>
@@ -1531,10 +1531,10 @@
         <v>34</v>
       </c>
       <c r="B26">
-        <v>20</v>
+        <v>11</v>
       </c>
       <c r="C26">
-        <v>20</v>
+        <v>11</v>
       </c>
       <c r="D26">
         <v>0</v>
@@ -1563,10 +1563,10 @@
         <v>35</v>
       </c>
       <c r="B27">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="C27">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="D27">
         <v>0</v>
@@ -1595,10 +1595,10 @@
         <v>36</v>
       </c>
       <c r="B28">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="C28">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="D28">
         <v>0</v>
@@ -1627,19 +1627,19 @@
         <v>37</v>
       </c>
       <c r="B29">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="C29">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="D29">
         <v>0</v>
       </c>
       <c r="E29">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F29">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G29">
         <v>0</v>
@@ -1659,10 +1659,10 @@
         <v>38</v>
       </c>
       <c r="B30">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="C30">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="D30">
         <v>0</v>
@@ -1691,10 +1691,10 @@
         <v>39</v>
       </c>
       <c r="B31">
-        <v>19</v>
+        <v>11</v>
       </c>
       <c r="C31">
-        <v>19</v>
+        <v>11</v>
       </c>
       <c r="D31">
         <v>0</v>
@@ -1746,10 +1746,10 @@
         <v>41</v>
       </c>
       <c r="B33">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="C33">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="D33">
         <v>0</v>
@@ -1778,10 +1778,10 @@
         <v>42</v>
       </c>
       <c r="B34">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="C34">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="D34">
         <v>0</v>
@@ -1810,10 +1810,10 @@
         <v>43</v>
       </c>
       <c r="B35">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="C35">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="D35">
         <v>0</v>
@@ -1842,10 +1842,10 @@
         <v>44</v>
       </c>
       <c r="B36">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="C36">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="D36">
         <v>0</v>
@@ -1874,10 +1874,10 @@
         <v>45</v>
       </c>
       <c r="B37">
-        <v>22</v>
+        <v>14</v>
       </c>
       <c r="C37">
-        <v>22</v>
+        <v>14</v>
       </c>
       <c r="D37">
         <v>0</v>
@@ -1906,10 +1906,10 @@
         <v>46</v>
       </c>
       <c r="B38">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="C38">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="D38">
         <v>1</v>
@@ -1938,10 +1938,10 @@
         <v>47</v>
       </c>
       <c r="B39">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="C39">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="D39">
         <v>0</v>
@@ -1970,10 +1970,10 @@
         <v>48</v>
       </c>
       <c r="B40">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="C40">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="D40">
         <v>1</v>
@@ -2002,10 +2002,10 @@
         <v>49</v>
       </c>
       <c r="B41">
-        <v>22</v>
+        <v>14</v>
       </c>
       <c r="C41">
-        <v>22</v>
+        <v>14</v>
       </c>
       <c r="D41">
         <v>0</v>
@@ -2034,13 +2034,13 @@
         <v>50</v>
       </c>
       <c r="B42">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="C42">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="D42">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E42">
         <v>5</v>
@@ -2066,19 +2066,19 @@
         <v>51</v>
       </c>
       <c r="B43">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="C43">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="D43">
         <v>0</v>
       </c>
       <c r="E43">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F43">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G43">
         <v>0</v>
@@ -2098,10 +2098,10 @@
         <v>52</v>
       </c>
       <c r="B44">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="C44">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="D44">
         <v>0</v>
@@ -2130,10 +2130,10 @@
         <v>53</v>
       </c>
       <c r="B45">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="C45">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="D45">
         <v>0</v>
@@ -2162,10 +2162,10 @@
         <v>54</v>
       </c>
       <c r="B46">
-        <v>22</v>
+        <v>12</v>
       </c>
       <c r="C46">
-        <v>22</v>
+        <v>12</v>
       </c>
       <c r="D46">
         <v>0</v>
@@ -2194,10 +2194,10 @@
         <v>55</v>
       </c>
       <c r="B47">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="C47">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="D47">
         <v>0</v>
@@ -2226,22 +2226,22 @@
         <v>56</v>
       </c>
       <c r="B48">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="C48">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="D48">
+        <v>3</v>
+      </c>
+      <c r="E48">
         <v>4</v>
       </c>
-      <c r="E48">
-        <v>5</v>
-      </c>
       <c r="F48">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="G48">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H48">
         <v>0.2557711225891841</v>
@@ -2258,10 +2258,10 @@
         <v>57</v>
       </c>
       <c r="B49">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="C49">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="D49">
         <v>1</v>
@@ -2290,13 +2290,13 @@
         <v>58</v>
       </c>
       <c r="B50">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="C50">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="D50">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E50">
         <v>6</v>
@@ -2322,10 +2322,10 @@
         <v>59</v>
       </c>
       <c r="B51">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="C51">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="D51">
         <v>0</v>
@@ -2354,10 +2354,10 @@
         <v>60</v>
       </c>
       <c r="B52">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="C52">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="D52">
         <v>0</v>
@@ -2386,10 +2386,10 @@
         <v>61</v>
       </c>
       <c r="B53">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="C53">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="D53">
         <v>1</v>
@@ -2418,10 +2418,10 @@
         <v>62</v>
       </c>
       <c r="B54">
-        <v>23</v>
+        <v>16</v>
       </c>
       <c r="C54">
-        <v>23</v>
+        <v>16</v>
       </c>
       <c r="D54">
         <v>1</v>
@@ -2450,22 +2450,22 @@
         <v>63</v>
       </c>
       <c r="B55">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="C55">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="D55">
         <v>1</v>
       </c>
       <c r="E55">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F55">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="G55">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H55">
         <v>0.7040554378759768</v>
@@ -2482,13 +2482,13 @@
         <v>64</v>
       </c>
       <c r="B56">
-        <v>20</v>
+        <v>11</v>
       </c>
       <c r="C56">
-        <v>19</v>
+        <v>11</v>
       </c>
       <c r="D56">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E56">
         <v>5</v>
@@ -2514,10 +2514,10 @@
         <v>65</v>
       </c>
       <c r="B57">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="C57">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="D57">
         <v>0</v>
@@ -2546,10 +2546,10 @@
         <v>66</v>
       </c>
       <c r="B58">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="C58">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="D58">
         <v>0</v>
@@ -2578,19 +2578,19 @@
         <v>67</v>
       </c>
       <c r="B59">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="C59">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="D59">
         <v>0</v>
       </c>
       <c r="E59">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F59">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G59">
         <v>0</v>
@@ -2610,10 +2610,10 @@
         <v>68</v>
       </c>
       <c r="B60">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="C60">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="D60">
         <v>0</v>
@@ -2642,13 +2642,13 @@
         <v>69</v>
       </c>
       <c r="B61">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="C61">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="D61">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E61">
         <v>3</v>
@@ -2674,19 +2674,19 @@
         <v>70</v>
       </c>
       <c r="B62">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="C62">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="D62">
         <v>1</v>
       </c>
       <c r="E62">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="F62">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="G62">
         <v>0</v>
@@ -2706,10 +2706,10 @@
         <v>71</v>
       </c>
       <c r="B63">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="C63">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="D63">
         <v>0</v>
@@ -2738,22 +2738,22 @@
         <v>72</v>
       </c>
       <c r="B64">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="C64">
-        <v>19</v>
+        <v>11</v>
       </c>
       <c r="D64">
+        <v>2</v>
+      </c>
+      <c r="E64">
+        <v>6</v>
+      </c>
+      <c r="F64">
+        <v>5</v>
+      </c>
+      <c r="G64">
         <v>1</v>
-      </c>
-      <c r="E64">
-        <v>6</v>
-      </c>
-      <c r="F64">
-        <v>6</v>
-      </c>
-      <c r="G64">
-        <v>0</v>
       </c>
       <c r="H64">
         <v>0.1274362090162726</v>
@@ -2770,10 +2770,10 @@
         <v>73</v>
       </c>
       <c r="B65">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="C65">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="D65">
         <v>0</v>
@@ -2825,10 +2825,10 @@
         <v>75</v>
       </c>
       <c r="B67">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="C67">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="D67">
         <v>0</v>
@@ -2857,19 +2857,19 @@
         <v>76</v>
       </c>
       <c r="B68">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="C68">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="D68">
         <v>0</v>
       </c>
       <c r="E68">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F68">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G68">
         <v>0</v>
@@ -2889,10 +2889,10 @@
         <v>77</v>
       </c>
       <c r="B69">
-        <v>22</v>
+        <v>14</v>
       </c>
       <c r="C69">
-        <v>22</v>
+        <v>14</v>
       </c>
       <c r="D69">
         <v>0</v>
@@ -2921,10 +2921,10 @@
         <v>78</v>
       </c>
       <c r="B70">
-        <v>22</v>
+        <v>14</v>
       </c>
       <c r="C70">
-        <v>22</v>
+        <v>14</v>
       </c>
       <c r="D70">
         <v>0</v>
@@ -2953,19 +2953,19 @@
         <v>79</v>
       </c>
       <c r="B71">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="C71">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="D71">
         <v>0</v>
       </c>
       <c r="E71">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F71">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G71">
         <v>0</v>
@@ -2985,10 +2985,10 @@
         <v>80</v>
       </c>
       <c r="B72">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="C72">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="D72">
         <v>0</v>
@@ -3017,19 +3017,19 @@
         <v>81</v>
       </c>
       <c r="B73">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="C73">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="D73">
         <v>0</v>
       </c>
       <c r="E73">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F73">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G73">
         <v>0</v>
@@ -3049,10 +3049,10 @@
         <v>82</v>
       </c>
       <c r="B74">
-        <v>19</v>
+        <v>11</v>
       </c>
       <c r="C74">
-        <v>19</v>
+        <v>11</v>
       </c>
       <c r="D74">
         <v>0</v>
@@ -3081,22 +3081,22 @@
         <v>83</v>
       </c>
       <c r="B75">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="C75">
-        <v>17</v>
+        <v>8</v>
       </c>
       <c r="D75">
+        <v>2</v>
+      </c>
+      <c r="E75">
+        <v>5</v>
+      </c>
+      <c r="F75">
+        <v>4</v>
+      </c>
+      <c r="G75">
         <v>1</v>
-      </c>
-      <c r="E75">
-        <v>5</v>
-      </c>
-      <c r="F75">
-        <v>5</v>
-      </c>
-      <c r="G75">
-        <v>0</v>
       </c>
       <c r="H75">
         <v>0.2228808701329766</v>
@@ -3113,13 +3113,13 @@
         <v>84</v>
       </c>
       <c r="B76">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="C76">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="D76">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E76">
         <v>5</v>
@@ -3145,10 +3145,10 @@
         <v>85</v>
       </c>
       <c r="B77">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="C77">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="D77">
         <v>0</v>
@@ -3177,19 +3177,19 @@
         <v>86</v>
       </c>
       <c r="B78">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="C78">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="D78">
         <v>0</v>
       </c>
       <c r="E78">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F78">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G78">
         <v>0</v>
@@ -3209,10 +3209,10 @@
         <v>87</v>
       </c>
       <c r="B79">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="C79">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="D79">
         <v>0</v>
@@ -3241,10 +3241,10 @@
         <v>88</v>
       </c>
       <c r="B80">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="C80">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="D80">
         <v>0</v>
@@ -3273,10 +3273,10 @@
         <v>89</v>
       </c>
       <c r="B81">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="C81">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="D81">
         <v>0</v>
@@ -3305,10 +3305,10 @@
         <v>90</v>
       </c>
       <c r="B82">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="C82">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="D82">
         <v>0</v>
@@ -3337,19 +3337,19 @@
         <v>91</v>
       </c>
       <c r="B83">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="C83">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="D83">
         <v>0</v>
       </c>
       <c r="E83">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F83">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G83">
         <v>0</v>
@@ -3369,10 +3369,10 @@
         <v>92</v>
       </c>
       <c r="B84">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="C84">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="D84">
         <v>0</v>
@@ -3401,19 +3401,19 @@
         <v>93</v>
       </c>
       <c r="B85">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="C85">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="D85">
         <v>0</v>
       </c>
       <c r="E85">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F85">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G85">
         <v>0</v>
@@ -3456,10 +3456,10 @@
         <v>95</v>
       </c>
       <c r="B87">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="C87">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="D87">
         <v>1</v>
@@ -3488,10 +3488,10 @@
         <v>96</v>
       </c>
       <c r="B88">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="C88">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="D88">
         <v>1</v>
@@ -3520,10 +3520,10 @@
         <v>97</v>
       </c>
       <c r="B89">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="C89">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="D89">
         <v>0</v>
@@ -3552,10 +3552,10 @@
         <v>98</v>
       </c>
       <c r="B90">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="C90">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="D90">
         <v>0</v>
@@ -3584,10 +3584,10 @@
         <v>99</v>
       </c>
       <c r="B91">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="C91">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="D91">
         <v>0</v>
@@ -3616,10 +3616,10 @@
         <v>100</v>
       </c>
       <c r="B92">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="C92">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="D92">
         <v>0</v>
@@ -3648,19 +3648,19 @@
         <v>101</v>
       </c>
       <c r="B93">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="C93">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="D93">
         <v>0</v>
       </c>
       <c r="E93">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F93">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G93">
         <v>0</v>
@@ -3680,10 +3680,10 @@
         <v>102</v>
       </c>
       <c r="B94">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="C94">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="D94">
         <v>0</v>
@@ -3712,10 +3712,10 @@
         <v>103</v>
       </c>
       <c r="B95">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="C95">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="D95">
         <v>0</v>
@@ -3744,10 +3744,10 @@
         <v>104</v>
       </c>
       <c r="B96">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="C96">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="D96">
         <v>0</v>
@@ -3776,10 +3776,10 @@
         <v>105</v>
       </c>
       <c r="B97">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="C97">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="D97">
         <v>3</v>
@@ -3808,19 +3808,19 @@
         <v>106</v>
       </c>
       <c r="B98">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="C98">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="D98">
         <v>0</v>
       </c>
       <c r="E98">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F98">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G98">
         <v>0</v>
@@ -3840,10 +3840,10 @@
         <v>107</v>
       </c>
       <c r="B99">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="C99">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="D99">
         <v>1</v>
@@ -3895,10 +3895,10 @@
         <v>109</v>
       </c>
       <c r="B101">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="C101">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="D101">
         <v>0</v>
@@ -3927,10 +3927,10 @@
         <v>110</v>
       </c>
       <c r="B102">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="C102">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="D102">
         <v>0</v>
@@ -3959,10 +3959,10 @@
         <v>111</v>
       </c>
       <c r="B103">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="C103">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="D103">
         <v>0</v>
@@ -4014,19 +4014,19 @@
         <v>113</v>
       </c>
       <c r="B105">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="C105">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="D105">
         <v>1</v>
       </c>
       <c r="E105">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F105">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G105">
         <v>0</v>
@@ -4046,10 +4046,10 @@
         <v>114</v>
       </c>
       <c r="B106">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="C106">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="D106">
         <v>0</v>
@@ -4078,10 +4078,10 @@
         <v>115</v>
       </c>
       <c r="B107">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="C107">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="D107">
         <v>0</v>
@@ -4110,10 +4110,10 @@
         <v>116</v>
       </c>
       <c r="B108">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="C108">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="D108">
         <v>0</v>
@@ -4142,10 +4142,10 @@
         <v>117</v>
       </c>
       <c r="B109">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="C109">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="D109">
         <v>0</v>
@@ -4174,10 +4174,10 @@
         <v>118</v>
       </c>
       <c r="B110">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="C110">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="D110">
         <v>0</v>
@@ -4206,10 +4206,10 @@
         <v>119</v>
       </c>
       <c r="B111">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="C111">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="D111">
         <v>0</v>
@@ -4238,10 +4238,10 @@
         <v>120</v>
       </c>
       <c r="B112">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="C112">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="D112">
         <v>0</v>
@@ -4270,10 +4270,10 @@
         <v>121</v>
       </c>
       <c r="B113">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="C113">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="D113">
         <v>1</v>
@@ -4302,10 +4302,10 @@
         <v>122</v>
       </c>
       <c r="B114">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="C114">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="D114">
         <v>2</v>
@@ -4334,19 +4334,19 @@
         <v>123</v>
       </c>
       <c r="B115">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="C115">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="D115">
         <v>0</v>
       </c>
       <c r="E115">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F115">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G115">
         <v>0</v>
@@ -4366,22 +4366,22 @@
         <v>124</v>
       </c>
       <c r="B116">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="C116">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D116">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E116">
         <v>4</v>
       </c>
       <c r="F116">
+        <v>1</v>
+      </c>
+      <c r="G116">
         <v>3</v>
-      </c>
-      <c r="G116">
-        <v>1</v>
       </c>
       <c r="H116">
         <v>0.7766696831301108</v>
@@ -4398,10 +4398,10 @@
         <v>125</v>
       </c>
       <c r="B117">
-        <v>22</v>
+        <v>14</v>
       </c>
       <c r="C117">
-        <v>22</v>
+        <v>14</v>
       </c>
       <c r="D117">
         <v>0</v>
@@ -4430,10 +4430,10 @@
         <v>126</v>
       </c>
       <c r="B118">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="C118">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="D118">
         <v>0</v>
@@ -4462,10 +4462,10 @@
         <v>127</v>
       </c>
       <c r="B119">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="C119">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="D119">
         <v>0</v>
@@ -4494,10 +4494,10 @@
         <v>128</v>
       </c>
       <c r="B120">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="C120">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="D120">
         <v>0</v>
